--- a/examples/dentiqueue/DentiQueue_financial_model.xlsx
+++ b/examples/dentiqueue/DentiQueue_financial_model.xlsx
@@ -2019,11 +2019,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="75228857"/>
-        <c:axId val="37867741"/>
+        <c:axId val="41115760"/>
+        <c:axId val="36598716"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="75228857"/>
+        <c:axId val="41115760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2056,7 +2056,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37867741"/>
+        <c:crossAx val="36598716"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2064,7 +2064,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37867741"/>
+        <c:axId val="36598716"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2107,7 +2107,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75228857"/>
+        <c:crossAx val="41115760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3405,11 +3405,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="69773431"/>
-        <c:axId val="35975788"/>
+        <c:axId val="20700888"/>
+        <c:axId val="30674801"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="69773431"/>
+        <c:axId val="20700888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3442,7 +3442,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35975788"/>
+        <c:crossAx val="30674801"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3450,7 +3450,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35975788"/>
+        <c:axId val="30674801"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3493,7 +3493,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69773431"/>
+        <c:crossAx val="20700888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4791,11 +4791,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="44713010"/>
-        <c:axId val="43923459"/>
+        <c:axId val="20951127"/>
+        <c:axId val="31573153"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="44713010"/>
+        <c:axId val="20951127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4828,7 +4828,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43923459"/>
+        <c:crossAx val="31573153"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4836,7 +4836,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43923459"/>
+        <c:axId val="31573153"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4879,7 +4879,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44713010"/>
+        <c:crossAx val="20951127"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
